--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121185386</v>
       </c>
       <c r="B5" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>121185437</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
+        <v>90657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B7" t="n">
-        <v>109995</v>
+        <v>90717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R7" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259899</v>
+        <v>121259859</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,7 +1402,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1419,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583937</v>
+        <v>583978</v>
       </c>
       <c r="R8" t="n">
-        <v>6397648</v>
+        <v>6397685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259859</v>
+        <v>121259882</v>
       </c>
       <c r="B9" t="n">
-        <v>90707</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,30 +1493,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1529,14 +1528,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583978</v>
+        <v>583953</v>
       </c>
       <c r="R9" t="n">
-        <v>6397685</v>
+        <v>6397655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1598,7 @@
         <v>121259923</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259882</v>
+        <v>121259839</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>110005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,48 +1726,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583953</v>
+        <v>584192</v>
       </c>
       <c r="R11" t="n">
-        <v>6397655</v>
+        <v>6397778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185386</v>
+        <v>121185437</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584100</v>
+        <v>584102</v>
       </c>
       <c r="R5" t="n">
         <v>6397775</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,12 +1109,18 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På anmärkningsvärd smal ek.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185437</v>
+        <v>121185386</v>
       </c>
       <c r="B6" t="n">
-        <v>90657</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,34 +1155,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584102</v>
+        <v>584100</v>
       </c>
       <c r="R6" t="n">
         <v>6397775</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,18 +1229,12 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På anmärkningsvärd smal ek.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259899</v>
+        <v>121259859</v>
       </c>
       <c r="B7" t="n">
         <v>90717</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583937</v>
+        <v>583978</v>
       </c>
       <c r="R7" t="n">
-        <v>6397648</v>
+        <v>6397685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259859</v>
+        <v>121259882</v>
       </c>
       <c r="B8" t="n">
-        <v>90717</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,30 +1379,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1414,14 +1414,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583978</v>
+        <v>583953</v>
       </c>
       <c r="R8" t="n">
-        <v>6397685</v>
+        <v>6397655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259882</v>
+        <v>121259923</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,49 +1493,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583953</v>
+        <v>583982</v>
       </c>
       <c r="R9" t="n">
-        <v>6397655</v>
+        <v>6397610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259923</v>
+        <v>121259899</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1608,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583982</v>
+        <v>583937</v>
       </c>
       <c r="R10" t="n">
-        <v>6397610</v>
+        <v>6397648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185437</v>
+        <v>121185386</v>
       </c>
       <c r="B5" t="n">
-        <v>90657</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1036,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584102</v>
+        <v>584100</v>
       </c>
       <c r="R5" t="n">
         <v>6397775</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,18 +1110,12 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På anmärkningsvärd smal ek.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185386</v>
+        <v>121185437</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>90669</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,35 +1150,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584100</v>
+        <v>584102</v>
       </c>
       <c r="R6" t="n">
         <v>6397775</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,12 +1223,18 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På anmärkningsvärd smal ek.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259859</v>
+        <v>121259923</v>
       </c>
       <c r="B7" t="n">
-        <v>90717</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1265,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583978</v>
+        <v>583982</v>
       </c>
       <c r="R7" t="n">
-        <v>6397685</v>
+        <v>6397610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259882</v>
+        <v>121259839</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
+        <v>110018</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,48 +1384,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>219677</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583953</v>
+        <v>584192</v>
       </c>
       <c r="R8" t="n">
-        <v>6397655</v>
+        <v>6397778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259923</v>
+        <v>121259882</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,50 +1495,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583982</v>
+        <v>583953</v>
       </c>
       <c r="R9" t="n">
-        <v>6397610</v>
+        <v>6397655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259899</v>
+        <v>121259859</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,7 +1632,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583937</v>
+        <v>583978</v>
       </c>
       <c r="R10" t="n">
-        <v>6397648</v>
+        <v>6397685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B11" t="n">
-        <v>110005</v>
+        <v>90729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R11" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185386</v>
+        <v>121185437</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584100</v>
+        <v>584102</v>
       </c>
       <c r="R5" t="n">
         <v>6397775</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,12 +1109,18 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På anmärkningsvärd smal ek.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185437</v>
+        <v>121185386</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,34 +1155,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584102</v>
+        <v>584100</v>
       </c>
       <c r="R6" t="n">
         <v>6397775</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,18 +1229,12 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På anmärkningsvärd smal ek.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>121259923</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B8" t="n">
-        <v>110018</v>
+        <v>90730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,39 +1380,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R8" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259882</v>
+        <v>121259859</v>
       </c>
       <c r="B9" t="n">
-        <v>91985</v>
+        <v>90730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,30 +1494,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1530,14 +1529,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583953</v>
+        <v>583978</v>
       </c>
       <c r="R9" t="n">
-        <v>6397655</v>
+        <v>6397685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259859</v>
+        <v>121259882</v>
       </c>
       <c r="B10" t="n">
-        <v>90729</v>
+        <v>91986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,30 +1608,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1644,14 +1643,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583978</v>
+        <v>583953</v>
       </c>
       <c r="R10" t="n">
-        <v>6397685</v>
+        <v>6397655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259899</v>
+        <v>121259839</v>
       </c>
       <c r="B11" t="n">
-        <v>90729</v>
+        <v>110019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1722,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583937</v>
+        <v>584192</v>
       </c>
       <c r="R11" t="n">
-        <v>6397648</v>
+        <v>6397778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185437</v>
+        <v>121185386</v>
       </c>
       <c r="B5" t="n">
-        <v>90670</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1036,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584102</v>
+        <v>584100</v>
       </c>
       <c r="R5" t="n">
         <v>6397775</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,18 +1110,12 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På anmärkningsvärd smal ek.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185386</v>
+        <v>121185437</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>90673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,35 +1150,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584100</v>
+        <v>584102</v>
       </c>
       <c r="R6" t="n">
         <v>6397775</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,12 +1223,18 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På anmärkningsvärd smal ek.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259923</v>
+        <v>121259839</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>110022</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,35 +1265,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583982</v>
+        <v>584192</v>
       </c>
       <c r="R7" t="n">
-        <v>6397610</v>
+        <v>6397778</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>121259899</v>
       </c>
       <c r="B8" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259859</v>
+        <v>121259923</v>
       </c>
       <c r="B9" t="n">
-        <v>90730</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1494,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1533,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583978</v>
+        <v>583982</v>
       </c>
       <c r="R9" t="n">
-        <v>6397685</v>
+        <v>6397610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259882</v>
+        <v>121259859</v>
       </c>
       <c r="B10" t="n">
-        <v>91986</v>
+        <v>90733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,30 +1609,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1643,14 +1644,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583953</v>
+        <v>583978</v>
       </c>
       <c r="R10" t="n">
-        <v>6397655</v>
+        <v>6397685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259839</v>
+        <v>121259882</v>
       </c>
       <c r="B11" t="n">
-        <v>110019</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,49 +1727,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219677</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584192</v>
+        <v>583953</v>
       </c>
       <c r="R11" t="n">
-        <v>6397778</v>
+        <v>6397655</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121185386</v>
+        <v>121185437</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>90673</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584100</v>
+        <v>584102</v>
       </c>
       <c r="R5" t="n">
         <v>6397775</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,12 +1109,18 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På anmärkningsvärd smal ek.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185437</v>
+        <v>121185386</v>
       </c>
       <c r="B6" t="n">
-        <v>90673</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,34 +1155,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584102</v>
+        <v>584100</v>
       </c>
       <c r="R6" t="n">
         <v>6397775</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,18 +1229,12 @@
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På anmärkningsvärd smal ek.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259899</v>
+        <v>121259923</v>
       </c>
       <c r="B8" t="n">
-        <v>90733</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,38 +1380,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583937</v>
+        <v>583982</v>
       </c>
       <c r="R8" t="n">
-        <v>6397648</v>
+        <v>6397610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259923</v>
+        <v>121259899</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>90733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1495,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583982</v>
+        <v>583937</v>
       </c>
       <c r="R9" t="n">
-        <v>6397610</v>
+        <v>6397648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>121185437</v>
       </c>
       <c r="B5" t="n">
-        <v>90673</v>
+        <v>90679</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>121185386</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B7" t="n">
-        <v>110022</v>
+        <v>90739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R7" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259923</v>
+        <v>121259839</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>110028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,35 +1379,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1420,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583982</v>
+        <v>584192</v>
       </c>
       <c r="R8" t="n">
-        <v>6397610</v>
+        <v>6397778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259899</v>
+        <v>121259923</v>
       </c>
       <c r="B9" t="n">
-        <v>90733</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,38 +1494,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583937</v>
+        <v>583982</v>
       </c>
       <c r="R9" t="n">
-        <v>6397648</v>
+        <v>6397610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1600,7 @@
         <v>121259859</v>
       </c>
       <c r="B10" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>121259882</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259899</v>
+        <v>121259859</v>
       </c>
       <c r="B7" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583937</v>
+        <v>583978</v>
       </c>
       <c r="R7" t="n">
-        <v>6397648</v>
+        <v>6397685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B8" t="n">
-        <v>110028</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,39 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R8" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259923</v>
+        <v>121259882</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,50 +1493,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583982</v>
+        <v>583953</v>
       </c>
       <c r="R9" t="n">
-        <v>6397610</v>
+        <v>6397655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259859</v>
+        <v>121259839</v>
       </c>
       <c r="B10" t="n">
-        <v>90739</v>
+        <v>110029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,38 +1607,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583978</v>
+        <v>584192</v>
       </c>
       <c r="R10" t="n">
-        <v>6397685</v>
+        <v>6397778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259882</v>
+        <v>121259923</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,49 +1722,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583953</v>
+        <v>583982</v>
       </c>
       <c r="R11" t="n">
-        <v>6397655</v>
+        <v>6397610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259859</v>
+        <v>121259923</v>
       </c>
       <c r="B7" t="n">
-        <v>90740</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1265,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583978</v>
+        <v>583982</v>
       </c>
       <c r="R7" t="n">
-        <v>6397685</v>
+        <v>6397610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259899</v>
+        <v>121259882</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,30 +1380,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1414,14 +1415,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583937</v>
+        <v>583953</v>
       </c>
       <c r="R8" t="n">
-        <v>6397648</v>
+        <v>6397655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259882</v>
+        <v>121259839</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>110029</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,48 +1498,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>219677</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583953</v>
+        <v>584192</v>
       </c>
       <c r="R9" t="n">
-        <v>6397655</v>
+        <v>6397778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1595,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B10" t="n">
-        <v>110029</v>
+        <v>90740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1609,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,13 +1648,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R10" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259923</v>
+        <v>121259859</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583982</v>
+        <v>583978</v>
       </c>
       <c r="R11" t="n">
-        <v>6397610</v>
+        <v>6397685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259923</v>
+        <v>121259882</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,50 +1265,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583982</v>
+        <v>583953</v>
       </c>
       <c r="R7" t="n">
-        <v>6397610</v>
+        <v>6397655</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121259882</v>
+        <v>121259923</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,49 +1379,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583953</v>
+        <v>583982</v>
       </c>
       <c r="R8" t="n">
-        <v>6397655</v>
+        <v>6397610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259899</v>
+        <v>121259859</v>
       </c>
       <c r="B10" t="n">
         <v>90740</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583937</v>
+        <v>583978</v>
       </c>
       <c r="R10" t="n">
-        <v>6397648</v>
+        <v>6397685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259859</v>
+        <v>121259899</v>
       </c>
       <c r="B11" t="n">
         <v>90740</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583978</v>
+        <v>583937</v>
       </c>
       <c r="R11" t="n">
-        <v>6397685</v>
+        <v>6397648</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121259882</v>
+        <v>121259859</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,30 +1265,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1300,14 +1300,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583953</v>
+        <v>583978</v>
       </c>
       <c r="R7" t="n">
-        <v>6397655</v>
+        <v>6397685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121259839</v>
+        <v>121259899</v>
       </c>
       <c r="B9" t="n">
-        <v>110029</v>
+        <v>90740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1494,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1534,13 +1533,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584192</v>
+        <v>583937</v>
       </c>
       <c r="R9" t="n">
-        <v>6397778</v>
+        <v>6397648</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259859</v>
+        <v>121259839</v>
       </c>
       <c r="B10" t="n">
-        <v>90740</v>
+        <v>110029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,38 +1608,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>219677</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583978</v>
+        <v>584192</v>
       </c>
       <c r="R10" t="n">
-        <v>6397685</v>
+        <v>6397778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259899</v>
+        <v>121259882</v>
       </c>
       <c r="B11" t="n">
-        <v>90740</v>
+        <v>91996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,30 +1723,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1758,14 +1758,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583937</v>
+        <v>583953</v>
       </c>
       <c r="R11" t="n">
-        <v>6397648</v>
+        <v>6397655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46954-2024 artfynd.xlsx
+++ b/artfynd/A 46954-2024 artfynd.xlsx
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121259839</v>
+        <v>121259882</v>
       </c>
       <c r="B10" t="n">
-        <v>110029</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,49 +1612,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 46954, Tjursbo, Sm</t>
+          <t>A 46954, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584192</v>
+        <v>583953</v>
       </c>
       <c r="R10" t="n">
-        <v>6397778</v>
+        <v>6397655</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121259882</v>
+        <v>121259839</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
+        <v>110029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,48 +1726,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46954, Sm</t>
+          <t>A 46954, Tjursbo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583953</v>
+        <v>584192</v>
       </c>
       <c r="R11" t="n">
-        <v>6397655</v>
+        <v>6397778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
